--- a/naver-place-crawler/results_health/남동구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/남동구_헬스장.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="Q2" t="n">
-        <v>850</v>
+        <v>872</v>
       </c>
       <c r="R2" t="n">
-        <v>1497</v>
+        <v>1528</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,42 +646,46 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>머슬앤피플 헬스&amp;PT 구월점</t>
+          <t>간석동PT 스포애니 간석오거리역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>merpygym@naver.com</t>
+          <t>spoany109@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1431-9618</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 성말로 9 이노프라자 4층 머슬앤피플</t>
+          <t>인천광역시 남동구 남동대로916번길 3 5층, 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/merpygym_fitness?igsh=bmNuZjJvMzJsOGJx</t>
+          <t>https://my.matterport.com/show/?m=589b1PD6bnt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>104</v>
+        <v>271</v>
       </c>
       <c r="Q3" t="n">
-        <v>1540</v>
+        <v>1311</v>
       </c>
       <c r="R3" t="n">
-        <v>1644</v>
+        <v>1582</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20585537</t>
+          <t>1775312302</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20585537</t>
+          <t>https://m.place.naver.com/place/1775312302</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -748,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이룸휘트니스&amp;필라테스</t>
+          <t>바로피트니스 인천논현점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eroom_fitness@naver.com</t>
+          <t>varofitness5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1389-9940</t>
+          <t>0507-1383-4480</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 호구포로 887 하나프라자 3층</t>
+          <t>인천광역시 남동구 논고개로 101 아름다운타워 11층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eroom_fitness</t>
+          <t>https://blog.naver.com/varofitness5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>114</v>
+        <v>1292</v>
       </c>
       <c r="Q4" t="n">
-        <v>643</v>
+        <v>1058</v>
       </c>
       <c r="R4" t="n">
-        <v>757</v>
+        <v>2350</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1892216586</t>
+          <t>1602318885</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892216586</t>
+          <t>https://m.place.naver.com/place/1602318885</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>여성전용PT복숭아헬스장</t>
+          <t>홍키통키 인천</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52997994@naver.com</t>
+          <t>pomati@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1417-8063</t>
+          <t>0507-1357-2217</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인주대로 588 대암빌딩 2층</t>
+          <t>인천광역시 남동구 소래역로 46 청호빌딩 5~6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://youtube.com//@복숭아헬스장</t>
+          <t>https://blog.naver.com/pomati</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -879,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -890,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>124</v>
+        <v>2533</v>
       </c>
       <c r="Q5" t="n">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="R5" t="n">
-        <v>451</v>
+        <v>2791</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2040870567</t>
+          <t>1022798841</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040870567</t>
+          <t>https://m.place.naver.com/place/1022798841</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -936,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>어게인핏 만수점 헬스장/PT</t>
+          <t>조이 휘트니스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>again_fit@naver.com</t>
+          <t>joy_gym_yk80@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1368-4028</t>
+          <t>032-469-1321</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 구월로 376 정은프라자 5층</t>
+          <t>인천광역시 남동구 만수로 47 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/again_fit</t>
+          <t>https://blog.naver.com/joy_gym_yk80</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>297</v>
+        <v>86</v>
       </c>
       <c r="Q6" t="n">
-        <v>989</v>
+        <v>29</v>
       </c>
       <c r="R6" t="n">
-        <v>1286</v>
+        <v>115</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1519553733</t>
+          <t>37332878</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1519553733</t>
+          <t>https://m.place.naver.com/place/37332878</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>구월동PT 시크릿짐</t>
+          <t>여성전용PT복숭아헬스장</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>secret_gym1@naver.com</t>
+          <t>52997994@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1380-1228</t>
+          <t>0507-1417-8063</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 용천로 80 201호,203호 시크릿짐</t>
+          <t>인천광역시 남동구 인주대로 588 대암빌딩 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/secret_gym1</t>
+          <t>https://youtube.com//@복숭아헬스장</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1067,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>237</v>
+        <v>125</v>
       </c>
       <c r="Q7" t="n">
-        <v>2326</v>
+        <v>337</v>
       </c>
       <c r="R7" t="n">
-        <v>2563</v>
+        <v>462</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,56 +1106,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>34698775</t>
+          <t>2040870567</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34698775</t>
+          <t>https://m.place.naver.com/place/2040870567</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>구월동PT AR퍼스널트레이닝</t>
+          <t>어게인핏 만수점 헬스장/PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>iooikjy@naver.com</t>
+          <t>again_fit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1309-9682</t>
+          <t>0507-1368-4028</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 구월남로 172 정락빌딩 4층</t>
+          <t>인천광역시 남동구 구월로 376 정은프라자 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://forms.gle/9LWpo2mBgZ2KYxDeA</t>
+          <t>https://blog.naver.com/again_fit</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1161,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>89</v>
+        <v>300</v>
       </c>
       <c r="Q8" t="n">
-        <v>943</v>
+        <v>1048</v>
       </c>
       <c r="R8" t="n">
-        <v>1032</v>
+        <v>1348</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>35652976</t>
+          <t>1519553733</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35652976</t>
+          <t>https://m.place.naver.com/place/1519553733</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1218,34 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>구월동PT 닥터피티</t>
+          <t>그리드짐 인천논현점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>doctor_pt@naver.com</t>
+          <t>gridgym2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1332-9682</t>
+          <t>0507-1382-9681</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 미래로 13 2층 204호</t>
+          <t>인천광역시 남동구 논고개로 77 8층 801호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/profile/c/doctorpt</t>
+          <t>https://blog.naver.com/gridgym2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1255,19 +1259,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>229</v>
+        <v>453</v>
       </c>
       <c r="Q9" t="n">
-        <v>375</v>
+        <v>620</v>
       </c>
       <c r="R9" t="n">
-        <v>604</v>
+        <v>1073</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1984264875</t>
+          <t>2011637820</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1984264875</t>
+          <t>https://m.place.naver.com/place/2011637820</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>그리드짐 인천논현점</t>
+          <t>구월동PT HP체형교정센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gridgym2@naver.com</t>
+          <t>chldudrb963@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1382-9681</t>
+          <t>0507-1404-7350</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 논고개로 77 8층 801호</t>
+          <t>인천광역시 남동구 구월로 223 5층 506호 HP체형교정센터</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gridgym2</t>
+          <t>https://blog.naver.com/chldudrb963</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>438</v>
+        <v>256</v>
       </c>
       <c r="Q10" t="n">
-        <v>612</v>
+        <v>251</v>
       </c>
       <c r="R10" t="n">
-        <v>1050</v>
+        <v>507</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2011637820</t>
+          <t>1178761113</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011637820</t>
+          <t>https://m.place.naver.com/place/1178761113</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>구월동PT 하이엔드휘트니스</t>
+          <t>필라테스 린 구월 아시아드점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>highendfit@naver.com</t>
+          <t>pilates0224@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>032-463-3396</t>
+          <t>0507-1412-0570</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 구월로 212 구월동 힐캐슬프라자 4층 하이엔드 구월점</t>
+          <t>인천 남동구 인하로 567 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://www.highendfitness.kr/default/</t>
+          <t>https://litt.ly/pilateslean_guwol_asiad</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,33 +1447,37 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wqicsli</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1870</v>
+        <v>137</v>
       </c>
       <c r="Q11" t="n">
-        <v>281</v>
+        <v>168</v>
       </c>
       <c r="R11" t="n">
-        <v>2151</v>
+        <v>305</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1068689800</t>
+          <t>2094037719</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1068689800</t>
+          <t>https://m.place.naver.com/place/2094037719</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/남동구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/남동구_헬스장.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="Q2" t="n">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="R2" t="n">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q3" t="n">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="R3" t="n">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바로피트니스 인천논현점</t>
+          <t>어게인핏 만수점 헬스장/PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>varofitness5@naver.com</t>
+          <t>again_fit@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1383-4480</t>
+          <t>0507-1368-4028</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 논고개로 101 아름다운타워 11층</t>
+          <t>인천광역시 남동구 구월로 376 정은프라자 5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/varofitness5</t>
+          <t>https://blog.naver.com/again_fit</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1292</v>
+        <v>300</v>
       </c>
       <c r="Q4" t="n">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="R4" t="n">
-        <v>2350</v>
+        <v>1355</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1602318885</t>
+          <t>1519553733</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602318885</t>
+          <t>https://m.place.naver.com/place/1519553733</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>홍키통키 인천</t>
+          <t>조이 휘트니스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pomati@naver.com</t>
+          <t>joy_gym_yk80@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1357-2217</t>
+          <t>032-469-1321</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 소래역로 46 청호빌딩 5~6층</t>
+          <t>인천광역시 남동구 만수로 47 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pomati</t>
+          <t>https://blog.naver.com/joy_gym_yk80</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -894,22 +894,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2533</v>
+        <v>86</v>
       </c>
       <c r="Q5" t="n">
-        <v>258</v>
+        <v>29</v>
       </c>
       <c r="R5" t="n">
-        <v>2791</v>
+        <v>115</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1022798841</t>
+          <t>37332878</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022798841</t>
+          <t>https://m.place.naver.com/place/37332878</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,39 +935,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>조이 휘트니스</t>
+          <t>여성전용PT복숭아헬스장</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>joy_gym_yk80@naver.com</t>
+          <t>52997994@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>032-469-1321</t>
+          <t>0507-1417-8063</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 만수로 47 5층</t>
+          <t>인천광역시 남동구 인주대로 588 대암빌딩 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/joy_gym_yk80</t>
+          <t>https://youtube.com//@복숭아헬스장</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="Q6" t="n">
-        <v>29</v>
+        <v>337</v>
       </c>
       <c r="R6" t="n">
-        <v>115</v>
+        <v>462</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37332878</t>
+          <t>2040870567</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37332878</t>
+          <t>https://m.place.naver.com/place/2040870567</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여성전용PT복숭아헬스장</t>
+          <t>그리드짐 인천논현점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52997994@naver.com</t>
+          <t>gridgym2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1417-8063</t>
+          <t>0507-1382-9681</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인주대로 588 대암빌딩 2층</t>
+          <t>인천광역시 남동구 논고개로 77 8층 801호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtube.com//@복숭아헬스장</t>
+          <t>https://blog.naver.com/gridgym2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>125</v>
+        <v>453</v>
       </c>
       <c r="Q7" t="n">
-        <v>337</v>
+        <v>620</v>
       </c>
       <c r="R7" t="n">
-        <v>462</v>
+        <v>1073</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2040870567</t>
+          <t>2011637820</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040870567</t>
+          <t>https://m.place.naver.com/place/2011637820</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,39 +1123,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>어게인핏 만수점 헬스장/PT</t>
+          <t>구월동PT 터닝포인트짐 여성전용점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>again_fit@naver.com</t>
+          <t>ksmturning@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1368-4028</t>
+          <t>0507-1448-9220</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 구월로 376 정은프라자 5층</t>
+          <t>인천광역시 남동구 구월로 243 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/again_fit</t>
+          <t>https://link.inpock.co.kr/turningpointgym_w_guweol</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>300</v>
+        <v>526</v>
       </c>
       <c r="Q8" t="n">
-        <v>1048</v>
+        <v>1635</v>
       </c>
       <c r="R8" t="n">
-        <v>1348</v>
+        <v>2161</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1519553733</t>
+          <t>1699032302</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1519553733</t>
+          <t>https://m.place.naver.com/place/1699032302</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>그리드짐 인천논현점</t>
+          <t>구월동PT HP체형교정센터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gridgym2@naver.com</t>
+          <t>chldudrb963@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1382-9681</t>
+          <t>0507-1404-7350</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 논고개로 77 8층 801호</t>
+          <t>인천광역시 남동구 구월로 223 5층 506호 HP체형교정센터</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gridgym2</t>
+          <t>https://blog.naver.com/chldudrb963</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>453</v>
+        <v>256</v>
       </c>
       <c r="Q9" t="n">
-        <v>620</v>
+        <v>252</v>
       </c>
       <c r="R9" t="n">
-        <v>1073</v>
+        <v>508</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2011637820</t>
+          <t>1178761113</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011637820</t>
+          <t>https://m.place.naver.com/place/1178761113</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,34 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>구월동PT HP체형교정센터</t>
+          <t>구월동PT 하이엔드휘트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chldudrb963@naver.com</t>
+          <t>highendfit@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1404-7350</t>
+          <t>032-463-3396</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 구월로 223 5층 506호 HP체형교정센터</t>
+          <t>인천광역시 남동구 구월로 212 구월동 힐캐슬프라자 4층 하이엔드 구월점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chldudrb963</t>
+          <t>http://www.highendfitness.kr/default/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1364,22 +1364,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>256</v>
+        <v>1879</v>
       </c>
       <c r="Q10" t="n">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="R10" t="n">
-        <v>507</v>
+        <v>2161</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1178761113</t>
+          <t>1068689800</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1178761113</t>
+          <t>https://m.place.naver.com/place/1068689800</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/남동구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/남동구_헬스장.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Q2" t="n">
         <v>870</v>
       </c>
       <c r="R2" t="n">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -841,34 +841,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>조이 휘트니스</t>
+          <t>여성전용PT복숭아헬스장</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>joy_gym_yk80@naver.com</t>
+          <t>52997994@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>032-469-1321</t>
+          <t>0507-1417-8063</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 만수로 47 5층</t>
+          <t>인천광역시 남동구 인주대로 588 대암빌딩 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/joy_gym_yk80</t>
+          <t>https://youtube.com//@복숭아헬스장</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>337</v>
       </c>
       <c r="R5" t="n">
-        <v>115</v>
+        <v>462</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37332878</t>
+          <t>2040870567</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37332878</t>
+          <t>https://m.place.naver.com/place/2040870567</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,39 +935,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>여성전용PT복숭아헬스장</t>
+          <t>머슬드래곤짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>52997994@naver.com</t>
+          <t>muscle_dragon_gym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1417-8063</t>
+          <t>0507-1349-0324</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인주대로 588 대암빌딩 2층</t>
+          <t>인천 남동구 소래역남로 22 에코프라자 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com//@복숭아헬스장</t>
+          <t>https://blog.naver.com/muscle_dragon_gym/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,15 +977,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40429</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>125</v>
+        <v>831</v>
       </c>
       <c r="Q6" t="n">
-        <v>337</v>
+        <v>498</v>
       </c>
       <c r="R6" t="n">
-        <v>462</v>
+        <v>1329</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2040870567</t>
+          <t>1537710869</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040870567</t>
+          <t>https://m.place.naver.com/place/1537710869</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1091,10 +1095,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q7" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="R7" t="n">
         <v>1073</v>
@@ -1239,7 +1243,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 구월로 223 5층 506호 HP체형교정센터</t>
+          <t>인천 남동구 구월로 223 5층 506호 HP체형교정센터</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,10 +1268,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wo3wbsv</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1333,7 +1341,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 구월로 212 구월동 힐캐슬프라자 4층 하이엔드 구월점</t>
+          <t>인천 남동구 구월로 212 구월동 힐캐슬프라자 4층 하이엔드 구월점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1358,10 +1366,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w480an</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>O</t>

--- a/naver-place-crawler/results_health/남동구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/남동구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Q2" t="n">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="R2" t="n">
-        <v>1533</v>
+        <v>1542</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q3" t="n">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="R3" t="n">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -812,10 +812,10 @@
         <v>301</v>
       </c>
       <c r="Q4" t="n">
-        <v>1063</v>
+        <v>1079</v>
       </c>
       <c r="R4" t="n">
-        <v>1364</v>
+        <v>1380</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,41 +834,41 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>여성전용PT복숭아헬스장</t>
+          <t>조이 휘트니스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52997994@naver.com</t>
+          <t>joy_gym_yk80@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1417-8063</t>
+          <t>032-469-1321</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인주대로 588 대암빌딩 2층</t>
+          <t>인천 남동구 만수로 47 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://youtube.com//@복숭아헬스장</t>
+          <t>https://blog.naver.com/joy_gym_yk80</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,15 +883,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4b2py5</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -899,17 +903,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="Q5" t="n">
-        <v>352</v>
+        <v>29</v>
       </c>
       <c r="R5" t="n">
-        <v>477</v>
+        <v>115</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +922,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2040870567</t>
+          <t>37332878</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040870567</t>
+          <t>https://m.place.naver.com/place/37332878</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>고다짐 인천논현점</t>
+          <t>여성전용PT복숭아헬스장</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>godagym_nh@naver.com</t>
+          <t>52997994@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1347-5466</t>
+          <t>0507-1417-8063</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 앵고개로847번길 50 토브타워 6층 602, 603, 604호</t>
+          <t>인천 남동구 인주대로 588 대암빌딩 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.godagym.com</t>
+          <t>https://youtube.com//@복숭아헬스장</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -982,13 +986,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wit7sbd</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>737</v>
+        <v>125</v>
       </c>
       <c r="Q6" t="n">
-        <v>1496</v>
+        <v>366</v>
       </c>
       <c r="R6" t="n">
-        <v>2233</v>
+        <v>491</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1233049459</t>
+          <t>2040870567</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1233049459</t>
+          <t>https://m.place.naver.com/place/2040870567</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1059,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 소래역로18번길 48 101호</t>
+          <t>인천 남동구 소래역로18번길 48 101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1084,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5itoe</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1094,10 +1106,10 @@
         <v>50</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1116,7 +1128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1157,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 논고개로123번길 17 아이플렉스 511호 엘리스휘트니스</t>
+          <t>인천 남동구 논고개로123번길 17 아이플렉스 511호 엘리스휘트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1170,10 +1182,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xasb</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q8" t="n">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="R8" t="n">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1210,7 +1226,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1279,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Q9" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="R9" t="n">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1304,7 +1320,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1398,105 +1414,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>필라테스 린 구월 아시아드점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>pilates0224@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1412-0570</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>인천 남동구 인하로 567 4층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://litt.ly/pilateslean_guwol_asiad</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wqicsli</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>169</v>
-      </c>
-      <c r="R11" t="n">
-        <v>307</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2094037719</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2094037719</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
